--- a/artfynd/A 57939-2025 artfynd.xlsx
+++ b/artfynd/A 57939-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113807108</v>
+        <v>107610879</v>
       </c>
       <c r="B2" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flasjötorp 100m N, Srm</t>
+          <t>Göranbotten, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607136</v>
+        <v>607155</v>
       </c>
       <c r="R2" t="n">
-        <v>6562974</v>
+        <v>6562970</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-03-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,22 +778,123 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Pontus Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Pontus Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113807108</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flasjötorp 100m N, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607136</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562974</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
